--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A57BC29-8BD6-4FCA-87D2-6A35F76A6C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5624AD95-A917-4590-ACA3-CB3E1D3477D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="1425" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="2655" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
   <si>
     <t>分類</t>
   </si>
@@ -915,7 +915,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1068,12 +1068,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1477,6 +1471,9 @@
       <c r="E3" s="39" t="s">
         <v>8</v>
       </c>
+      <c r="G3" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="H3" s="36" t="s">
         <v>73</v>
       </c>
@@ -1787,7 +1784,7 @@
       <c r="H22" s="52"/>
     </row>
     <row r="23" spans="2:8" ht="18.75">
-      <c r="B23" s="54" t="s">
+      <c r="B23" t="s">
         <v>79</v>
       </c>
       <c r="C23"/>
@@ -1798,7 +1795,7 @@
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="2:8" ht="18.75">
-      <c r="B24" s="55" t="s">
+      <c r="B24" t="s">
         <v>80</v>
       </c>
       <c r="C24"/>
@@ -1809,7 +1806,7 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:8" ht="18.75">
-      <c r="B25" s="55" t="s">
+      <c r="B25" t="s">
         <v>78</v>
       </c>
       <c r="C25"/>
@@ -1820,7 +1817,7 @@
       <c r="H25" s="6"/>
     </row>
     <row r="26" spans="2:8" ht="18.75">
-      <c r="B26" s="55" t="s">
+      <c r="B26" t="s">
         <v>81</v>
       </c>
       <c r="C26"/>
@@ -2533,7 +2530,7 @@
       </c>
       <c r="E3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "作業中")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
@@ -2584,7 +2581,7 @@
       </c>
       <c r="J4" s="13">
         <f ca="1">NETWORKDAYS(J5,J6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="13">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
@@ -2656,7 +2653,7 @@
       </c>
       <c r="J6" s="26">
         <f ca="1">TODAY()</f>
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="12"/>
@@ -2879,6 +2876,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3016,22 +3028,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3047,21 +3061,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5624AD95-A917-4590-ACA3-CB3E1D3477D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F35BB3-57CC-4F7F-9C8A-9E4EDEA449DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="2655" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="82">
   <si>
     <t>分類</t>
   </si>
@@ -608,7 +608,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -669,6 +669,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="20">
     <border>
@@ -1067,7 +1073,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1491,6 +1497,9 @@
       <c r="E4" s="39" t="s">
         <v>13</v>
       </c>
+      <c r="G4" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H4" s="36"/>
     </row>
     <row r="5" spans="2:8" ht="18.75">
@@ -1506,6 +1515,9 @@
       <c r="E5" s="39" t="s">
         <v>13</v>
       </c>
+      <c r="G5" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H5" s="36" t="s">
         <v>49</v>
       </c>
@@ -1524,7 +1536,9 @@
         <v>8</v>
       </c>
       <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
+      <c r="G6" s="40" t="s">
+        <v>9</v>
+      </c>
       <c r="H6" s="45" t="s">
         <v>53</v>
       </c>
@@ -1543,7 +1557,9 @@
         <v>13</v>
       </c>
       <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
+      <c r="G7" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H7" s="42"/>
     </row>
     <row r="8" spans="2:8" ht="18.75">
@@ -1559,6 +1575,9 @@
       <c r="E8" s="39" t="s">
         <v>8</v>
       </c>
+      <c r="G8" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H8" s="36"/>
     </row>
     <row r="9" spans="2:8" ht="18.75">
@@ -1574,6 +1593,9 @@
       <c r="E9" s="39" t="s">
         <v>13</v>
       </c>
+      <c r="G9" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H9" s="36" t="s">
         <v>61</v>
       </c>
@@ -1591,6 +1613,9 @@
       <c r="E10" s="39" t="s">
         <v>8</v>
       </c>
+      <c r="G10" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H10" s="43" t="s">
         <v>56</v>
       </c>
@@ -1608,6 +1633,9 @@
       <c r="E11" s="39" t="s">
         <v>8</v>
       </c>
+      <c r="G11" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H11" s="43" t="s">
         <v>59</v>
       </c>
@@ -1625,6 +1653,9 @@
       <c r="E12" s="39" t="s">
         <v>8</v>
       </c>
+      <c r="G12" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H12" s="43" t="s">
         <v>60</v>
       </c>
@@ -1642,6 +1673,9 @@
       <c r="E13" s="39" t="s">
         <v>8</v>
       </c>
+      <c r="G13" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H13" s="43"/>
     </row>
     <row r="14" spans="2:8" ht="38.25" thickBot="1">
@@ -1658,7 +1692,9 @@
         <v>8</v>
       </c>
       <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
+      <c r="G14" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H14" s="46" t="s">
         <v>57</v>
       </c>
@@ -1677,7 +1713,9 @@
         <v>13</v>
       </c>
       <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="G15" s="38" t="s">
+        <v>9</v>
+      </c>
       <c r="H15" s="42"/>
     </row>
     <row r="16" spans="2:8" ht="18.75">
@@ -1693,6 +1731,9 @@
       <c r="E16" s="39" t="s">
         <v>13</v>
       </c>
+      <c r="G16" s="39" t="s">
+        <v>9</v>
+      </c>
       <c r="H16" s="36"/>
     </row>
     <row r="17" spans="2:8" ht="18.75">
@@ -1707,6 +1748,9 @@
       </c>
       <c r="E17" s="39" t="s">
         <v>13</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="H17" s="36" t="s">
         <v>62</v>
@@ -1718,7 +1762,9 @@
       <c r="D18" s="40"/>
       <c r="E18" s="40"/>
       <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
+      <c r="G18" s="40" t="s">
+        <v>9</v>
+      </c>
       <c r="H18" s="37"/>
     </row>
     <row r="19" spans="2:8" ht="19.5" thickBot="1">
@@ -1735,7 +1781,9 @@
         <v>8</v>
       </c>
       <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
+      <c r="G19" s="50" t="s">
+        <v>9</v>
+      </c>
       <c r="H19" s="51"/>
     </row>
     <row r="20" spans="2:8" ht="19.5" thickBot="1">
@@ -1752,7 +1800,9 @@
         <v>13</v>
       </c>
       <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
+      <c r="G20" s="50" t="s">
+        <v>9</v>
+      </c>
       <c r="H20" s="51" t="s">
         <v>76</v>
       </c>
@@ -1763,11 +1813,13 @@
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="50">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E21" s="50"/>
       <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
+      <c r="G21" s="50" t="s">
+        <v>9</v>
+      </c>
       <c r="H21" s="52"/>
     </row>
     <row r="22" spans="2:8" ht="19.5" thickBot="1">
@@ -1776,11 +1828,13 @@
       </c>
       <c r="C22" s="49"/>
       <c r="D22" s="50">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E22" s="50"/>
       <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
+      <c r="G22" s="50" t="s">
+        <v>9</v>
+      </c>
       <c r="H22" s="52"/>
     </row>
     <row r="23" spans="2:8" ht="18.75">
@@ -2510,7 +2564,7 @@
       </c>
       <c r="J2" s="13">
         <f>SUM(C:C)</f>
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K2" s="13"/>
       <c r="L2" s="12"/>
@@ -2534,7 +2588,7 @@
       </c>
       <c r="F3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G3" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
@@ -2561,16 +2615,16 @@
         <v>8</v>
       </c>
       <c r="D4" s="28">
-        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵ベース", コスト表!G:G, "完了")</f>
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "完了")</f>
         <v>0</v>
       </c>
       <c r="E4" s="28">
-        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵ベース", コスト表!G:G, "作業中")</f>
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
       <c r="F4" s="28">
-        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵ベース", コスト表!G:G, "未着手")</f>
-        <v>0</v>
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "未着手")</f>
+        <v>8</v>
       </c>
       <c r="G4" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵") * 100,1)</f>
@@ -2598,16 +2652,16 @@
         <v>2</v>
       </c>
       <c r="D5" s="28">
-        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "完了")</f>
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "Boss", コスト表!G:G, "完了")</f>
         <v>0</v>
       </c>
       <c r="E5" s="28">
-        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "作業中")</f>
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "Boss", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
       <c r="F5" s="28">
-        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "未着手")</f>
-        <v>0</v>
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "Boss", コスト表!G:G, "未着手")</f>
+        <v>2</v>
       </c>
       <c r="G5" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "Boss", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "Boss") * 100,1)</f>
@@ -2633,16 +2687,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="28">
-        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵2(ランナーゾンビ)", コスト表!G:G, "完了")</f>
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ステージ", コスト表!G:G, "完了")</f>
         <v>0</v>
       </c>
       <c r="E6" s="28">
-        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵2(ランナーゾンビ)", コスト表!G:G, "作業中")</f>
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ステージ", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
       <c r="F6" s="28">
-        <f>SUMIFS(コスト表!D:D,コスト表!B:B,"敵2(ランナーゾンビ)",コスト表!G:G,"未着手")</f>
-        <v>0</v>
+        <f>SUMIFS(コスト表!D:D,コスト表!B:B,"ステージ",コスト表!G:G,"未着手")</f>
+        <v>1</v>
       </c>
       <c r="G6" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "ステージ", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "ステージ") * 100,1)</f>
@@ -2667,10 +2721,22 @@
         <f>SUMIF(コスト表!B:B, B7, コスト表!D:D)</f>
         <v>2</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="24"/>
+      <c r="D7" s="28">
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "チュートリアル", コスト表!G:G, "完了")</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="28">
+        <f>SUMIFS(コスト表!D:D, コスト表!B:B, "チュートリアル", コスト表!G:G, "作業中")</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="28">
+        <f>SUMIFS(コスト表!D:D,コスト表!B:B,"チュートリアル",コスト表!G:G,"未着手")</f>
+        <v>2</v>
+      </c>
+      <c r="G7" s="24">
+        <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "チュートリアル", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "チュートリアル") * 100,1)</f>
+        <v>0</v>
+      </c>
       <c r="I7" s="53"/>
       <c r="J7" s="26"/>
       <c r="K7" s="26"/>
@@ -2683,7 +2749,7 @@
       </c>
       <c r="C8" s="8">
         <f>SUMIF(コスト表!B:B, B8, コスト表!D:D)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D8" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵3(遠距離型ゾンビ)", コスト表!G:G, "完了")</f>
@@ -2709,7 +2775,7 @@
       </c>
       <c r="C9" s="8">
         <f>SUMIF(コスト表!B:B, B9, コスト表!D:D)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D9" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ボス(ゾンビを召喚)", コスト表!G:G, "完了")</f>
@@ -2876,21 +2942,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3028,24 +3079,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3061,4 +3110,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F35BB3-57CC-4F7F-9C8A-9E4EDEA449DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84B8413-3ADB-4432-B02C-7394CAE8CEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="2655" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="83">
   <si>
     <t>分類</t>
   </si>
@@ -508,6 +508,28 @@
       <t>ヌ</t>
     </rPh>
     <rPh sb="20" eb="23">
+      <t>フグアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠距離攻撃で射線が通っていない状態で攻撃をしてくる不具合</t>
+    <rPh sb="0" eb="5">
+      <t>エンキョリコウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シャセン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
       <t>フグアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1882,6 +1904,9 @@
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="2:8" ht="18.75">
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
       <c r="C27"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -2942,6 +2967,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3079,22 +3119,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3110,21 +3152,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84B8413-3ADB-4432-B02C-7394CAE8CEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F5E5F0-BC27-43D8-AAB0-BFCA51DCD117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="2655" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="2655" windowWidth="24600" windowHeight="11025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="プルダウン用" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">集計!$B$2:$G$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="86">
   <si>
     <t>分類</t>
   </si>
@@ -531,6 +531,27 @@
     </rPh>
     <rPh sb="25" eb="28">
       <t>フグアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自動武器切り替え</t>
+    <rPh sb="0" eb="5">
+      <t>ジドウブキキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タックル攻撃後のノックバック</t>
+    <rPh sb="4" eb="7">
+      <t>コウゲキゴ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1439,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I103"/>
+  <dimension ref="B1:I105"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -1544,93 +1565,91 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="38.25" thickBot="1">
-      <c r="B6" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="40">
-        <v>3</v>
-      </c>
-      <c r="E6" s="40" t="s">
+    <row r="6" spans="2:8" ht="18.75">
+      <c r="B6" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="45" t="s">
-        <v>53</v>
-      </c>
+      <c r="H6" s="36"/>
     </row>
     <row r="7" spans="2:8" ht="18.75">
-      <c r="B7" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="38">
+      <c r="B7" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="39">
         <v>1</v>
       </c>
-      <c r="E7" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="38"/>
+      <c r="E7" s="39" t="s">
+        <v>8</v>
+      </c>
       <c r="G7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="42"/>
-    </row>
-    <row r="8" spans="2:8" ht="18.75">
-      <c r="B8" s="34" t="s">
+      <c r="H7" s="36"/>
+    </row>
+    <row r="8" spans="2:8" ht="38.25" thickBot="1">
+      <c r="B8" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="40">
+        <v>3</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="18.75">
+      <c r="B9" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="36"/>
-    </row>
-    <row r="9" spans="2:8" ht="18.75">
-      <c r="B9" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="39" t="s">
+      <c r="C9" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="38">
+        <v>1</v>
+      </c>
+      <c r="E9" s="38" t="s">
         <v>13</v>
       </c>
+      <c r="F9" s="38"/>
       <c r="G9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="36" t="s">
-        <v>61</v>
-      </c>
+      <c r="H9" s="42"/>
     </row>
     <row r="10" spans="2:8" ht="18.75">
       <c r="B10" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="43" t="s">
-        <v>54</v>
+      <c r="C10" s="36" t="s">
+        <v>46</v>
       </c>
       <c r="D10" s="39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="39" t="s">
         <v>8</v>
@@ -1638,28 +1657,26 @@
       <c r="G10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="43" t="s">
-        <v>56</v>
-      </c>
+      <c r="H10" s="36"/>
     </row>
     <row r="11" spans="2:8" ht="18.75">
       <c r="B11" s="34" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D11" s="39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G11" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="43" t="s">
-        <v>59</v>
+      <c r="H11" s="36" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="18.75">
@@ -1667,7 +1684,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D12" s="39">
         <v>1</v>
@@ -1679,15 +1696,15 @@
         <v>9</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="18.75">
       <c r="B13" s="34" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D13" s="39">
         <v>1</v>
@@ -1698,192 +1715,210 @@
       <c r="G13" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="43"/>
-    </row>
-    <row r="14" spans="2:8" ht="38.25" thickBot="1">
-      <c r="B14" s="35" t="s">
+      <c r="H13" s="43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="18.75">
+      <c r="B14" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="40">
-        <v>2</v>
-      </c>
-      <c r="E14" s="40" t="s">
+      <c r="C14" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="39">
+        <v>1</v>
+      </c>
+      <c r="E14" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="40"/>
       <c r="G14" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="46" t="s">
-        <v>57</v>
+      <c r="H14" s="43" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="18.75">
-      <c r="B15" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="38">
+      <c r="B15" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="39">
         <v>1</v>
       </c>
-      <c r="E15" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38" t="s">
+      <c r="E15" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="42"/>
-    </row>
-    <row r="16" spans="2:8" ht="18.75">
-      <c r="B16" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>13</v>
-      </c>
+      <c r="H15" s="43"/>
+    </row>
+    <row r="16" spans="2:8" ht="38.25" thickBot="1">
+      <c r="B16" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="40">
+        <v>2</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="36"/>
+      <c r="H16" s="46" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="17" spans="2:8" ht="18.75">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="38">
+        <v>1</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="42"/>
+    </row>
+    <row r="18" spans="2:8" ht="18.75">
+      <c r="B18" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C18" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="36"/>
+    </row>
+    <row r="19" spans="2:8" ht="18.75">
+      <c r="B19" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D19" s="39">
         <v>0.5</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E19" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G19" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="36" t="s">
+      <c r="H19" s="36" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="19.5" thickBot="1">
-      <c r="B18" s="35"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40" t="s">
+    <row r="20" spans="2:8" ht="19.5" thickBot="1">
+      <c r="B20" s="35"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="37"/>
-    </row>
-    <row r="19" spans="2:8" ht="19.5" thickBot="1">
-      <c r="B19" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="50">
-        <v>1</v>
-      </c>
-      <c r="E19" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="51"/>
-    </row>
-    <row r="20" spans="2:8" ht="19.5" thickBot="1">
-      <c r="B20" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" s="50">
-        <v>2</v>
-      </c>
-      <c r="E20" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="51" t="s">
-        <v>76</v>
-      </c>
+      <c r="H20" s="37"/>
     </row>
     <row r="21" spans="2:8" ht="19.5" thickBot="1">
       <c r="B21" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>51</v>
+      </c>
       <c r="D21" s="50">
-        <v>0</v>
-      </c>
-      <c r="E21" s="50"/>
+        <v>1</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>8</v>
+      </c>
       <c r="F21" s="50"/>
       <c r="G21" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="52"/>
+      <c r="H21" s="51"/>
     </row>
     <row r="22" spans="2:8" ht="19.5" thickBot="1">
-      <c r="B22" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="49"/>
+      <c r="B22" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>75</v>
+      </c>
       <c r="D22" s="50">
-        <v>0</v>
-      </c>
-      <c r="E22" s="50"/>
+        <v>2</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>13</v>
+      </c>
       <c r="F22" s="50"/>
       <c r="G22" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="H22" s="52"/>
-    </row>
-    <row r="23" spans="2:8" ht="18.75">
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="2:8" ht="18.75">
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="6"/>
+      <c r="H22" s="51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="19.5" thickBot="1">
+      <c r="B23" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="49"/>
+      <c r="D23" s="50">
+        <v>0</v>
+      </c>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="52"/>
+    </row>
+    <row r="24" spans="2:8" ht="19.5" thickBot="1">
+      <c r="B24" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="49"/>
+      <c r="D24" s="50">
+        <v>0</v>
+      </c>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="52"/>
     </row>
     <row r="25" spans="2:8" ht="18.75">
       <c r="B25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="4"/>
@@ -1894,7 +1929,7 @@
     </row>
     <row r="26" spans="2:8" ht="18.75">
       <c r="B26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26"/>
       <c r="D26" s="4"/>
@@ -1905,7 +1940,7 @@
     </row>
     <row r="27" spans="2:8" ht="18.75">
       <c r="B27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C27"/>
       <c r="D27" s="4"/>
@@ -1915,6 +1950,9 @@
       <c r="H27" s="6"/>
     </row>
     <row r="28" spans="2:8" ht="18.75">
+      <c r="B28" t="s">
+        <v>81</v>
+      </c>
       <c r="C28"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -1923,6 +1961,9 @@
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="2:8" ht="18.75">
+      <c r="B29" t="s">
+        <v>82</v>
+      </c>
       <c r="C29"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -2219,7 +2260,7 @@
       <c r="H65" s="6"/>
     </row>
     <row r="66" spans="3:8" ht="18.75">
-      <c r="C66" s="6"/>
+      <c r="C66"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
@@ -2235,7 +2276,7 @@
       <c r="H67" s="6"/>
     </row>
     <row r="68" spans="3:8" ht="18.75">
-      <c r="C68"/>
+      <c r="C68" s="6"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
@@ -2435,20 +2476,20 @@
       <c r="H92" s="6"/>
     </row>
     <row r="93" spans="3:8" ht="18.75">
-      <c r="C93" s="4"/>
-      <c r="D93" s="47"/>
+      <c r="C93"/>
+      <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
+      <c r="H93" s="6"/>
     </row>
     <row r="94" spans="3:8" ht="18.75">
-      <c r="C94" s="4"/>
-      <c r="D94" s="47"/>
+      <c r="C94"/>
+      <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
+      <c r="H94" s="6"/>
     </row>
     <row r="95" spans="3:8" ht="18.75">
       <c r="C95" s="4"/>
@@ -2467,24 +2508,24 @@
       <c r="H96" s="4"/>
     </row>
     <row r="97" spans="3:8" ht="18.75">
-      <c r="C97"/>
-      <c r="D97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="47"/>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
-      <c r="H97" s="6"/>
+      <c r="H97" s="4"/>
     </row>
     <row r="98" spans="3:8" ht="18.75">
-      <c r="C98"/>
-      <c r="D98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="47"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
-      <c r="H98" s="6"/>
+      <c r="H98" s="4"/>
     </row>
     <row r="99" spans="3:8" ht="18.75">
-      <c r="C99" s="4"/>
-      <c r="D99" s="47"/>
+      <c r="C99"/>
+      <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
@@ -2499,25 +2540,41 @@
       <c r="H100" s="6"/>
     </row>
     <row r="101" spans="3:8" ht="18.75">
-      <c r="C101"/>
-      <c r="D101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="47"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
       <c r="H101" s="6"/>
     </row>
     <row r="102" spans="3:8" ht="18.75">
-      <c r="C102" s="43"/>
-      <c r="D102" s="39"/>
-      <c r="H102" s="36"/>
+      <c r="C102"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="6"/>
     </row>
     <row r="103" spans="3:8" ht="18.75">
-      <c r="C103" s="43"/>
-      <c r="D103" s="39"/>
-      <c r="H103" s="36"/>
+      <c r="C103"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="6"/>
+    </row>
+    <row r="104" spans="3:8" ht="18.75">
+      <c r="C104" s="43"/>
+      <c r="D104" s="39"/>
+      <c r="H104" s="36"/>
+    </row>
+    <row r="105" spans="3:8" ht="18.75">
+      <c r="C105" s="43"/>
+      <c r="D105" s="39"/>
+      <c r="H105" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="E2:G103" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E2:G105" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -2528,19 +2585,19 @@
           <x14:formula1>
             <xm:f>プルダウン用!$B$3:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G97:G98 G100:G1048576 G1:G92</xm:sqref>
+          <xm:sqref>G99:G100 G102:G1048576 G1:G94</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
             <xm:f>プルダウン用!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F100:F1048576 F1:F98</xm:sqref>
+          <xm:sqref>F102:F1048576 F1:F100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
             <xm:f>プルダウン用!$F$3:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E97:E98 E100:E1048576 E1:E92</xm:sqref>
+          <xm:sqref>E99:E100 E102:E1048576 E1:E94</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2589,7 +2646,7 @@
       </c>
       <c r="J2" s="13">
         <f>SUM(C:C)</f>
-        <v>21</v>
+        <v>22.5</v>
       </c>
       <c r="K2" s="13"/>
       <c r="L2" s="12"/>
@@ -2601,7 +2658,7 @@
       </c>
       <c r="C3" s="8">
         <f>SUMIF(コスト表!B:B, B3, コスト表!D:D)</f>
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="D3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "完了")</f>
@@ -2613,7 +2670,7 @@
       </c>
       <c r="F3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="G3" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
@@ -2967,21 +3024,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3119,24 +3161,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3152,4 +3192,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F5E5F0-BC27-43D8-AAB0-BFCA51DCD117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF02CE9-A0FC-452A-9A65-33A37A1730B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="2655" windowWidth="24600" windowHeight="11025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="2655" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="90">
   <si>
     <t>分類</t>
   </si>
@@ -552,6 +552,97 @@
     <t>タックル攻撃後のノックバック</t>
     <rPh sb="4" eb="7">
       <t>コウゲキゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が湧く位置を各ウェーブで固定化し常に敵が何体いるというように設計する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>コテイカ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツネ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナンタイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面サイズを変更した際のリザルトシーンUI調整</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>射撃タスクチュートリアルでショットガンで敵を倒した際タスクカウントが進まない不具合</t>
+    <rPh sb="0" eb="2">
+      <t>シャゲキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="38" eb="41">
+      <t>フグアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ショットガンで倒した際吹き飛んで死なないことがある不具合</t>
+    <rPh sb="7" eb="8">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>フグアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1972,6 +2063,9 @@
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="2:8" ht="18.75">
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
       <c r="C30"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -1980,6 +2074,9 @@
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="2:8" ht="18.75">
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
       <c r="C31"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -1988,6 +2085,9 @@
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="2:8" ht="18.75">
+      <c r="B32" t="s">
+        <v>88</v>
+      </c>
       <c r="C32"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -1995,7 +2095,10 @@
       <c r="G32" s="4"/>
       <c r="H32" s="6"/>
     </row>
-    <row r="33" spans="3:8" ht="18.75">
+    <row r="33" spans="2:8" ht="18.75">
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
       <c r="C33"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -2003,7 +2106,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="6"/>
     </row>
-    <row r="34" spans="3:8" ht="18.75">
+    <row r="34" spans="2:8" ht="18.75">
       <c r="C34"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -2011,7 +2114,7 @@
       <c r="G34" s="4"/>
       <c r="H34" s="6"/>
     </row>
-    <row r="35" spans="3:8" ht="18.75">
+    <row r="35" spans="2:8" ht="18.75">
       <c r="C35"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -2019,7 +2122,7 @@
       <c r="G35" s="4"/>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="3:8" ht="18.75">
+    <row r="36" spans="2:8" ht="18.75">
       <c r="C36"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -2027,7 +2130,7 @@
       <c r="G36" s="4"/>
       <c r="H36" s="6"/>
     </row>
-    <row r="37" spans="3:8" ht="18.75">
+    <row r="37" spans="2:8" ht="18.75">
       <c r="C37"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -2035,7 +2138,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="3:8" ht="18.75">
+    <row r="38" spans="2:8" ht="18.75">
       <c r="C38"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -2043,7 +2146,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="3:8" ht="18.75">
+    <row r="39" spans="2:8" ht="18.75">
       <c r="C39"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -2051,7 +2154,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="3:8" ht="18.75">
+    <row r="40" spans="2:8" ht="18.75">
       <c r="C40"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -2059,7 +2162,7 @@
       <c r="G40" s="4"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="3:8" ht="18.75">
+    <row r="41" spans="2:8" ht="18.75">
       <c r="C41"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2067,7 +2170,7 @@
       <c r="G41" s="4"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="3:8" ht="18.75">
+    <row r="42" spans="2:8" ht="18.75">
       <c r="C42"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -2075,7 +2178,7 @@
       <c r="G42" s="4"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="3:8" ht="18.75">
+    <row r="43" spans="2:8" ht="18.75">
       <c r="C43"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -2083,7 +2186,7 @@
       <c r="G43" s="4"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="3:8" ht="18.75">
+    <row r="44" spans="2:8" ht="18.75">
       <c r="C44"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -2091,7 +2194,7 @@
       <c r="G44" s="4"/>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="3:8" ht="18.75">
+    <row r="45" spans="2:8" ht="18.75">
       <c r="C45"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -2099,7 +2202,7 @@
       <c r="G45" s="4"/>
       <c r="H45" s="6"/>
     </row>
-    <row r="46" spans="3:8" ht="18.75">
+    <row r="46" spans="2:8" ht="18.75">
       <c r="C46"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -2107,7 +2210,7 @@
       <c r="G46" s="4"/>
       <c r="H46" s="6"/>
     </row>
-    <row r="47" spans="3:8" ht="18.75">
+    <row r="47" spans="2:8" ht="18.75">
       <c r="C47"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -2115,7 +2218,7 @@
       <c r="G47" s="4"/>
       <c r="H47" s="6"/>
     </row>
-    <row r="48" spans="3:8" ht="18.75">
+    <row r="48" spans="2:8" ht="18.75">
       <c r="C48"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -2717,7 +2820,7 @@
       </c>
       <c r="J4" s="13">
         <f ca="1">NETWORKDAYS(J5,J6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="13">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
@@ -2789,7 +2892,7 @@
       </c>
       <c r="J6" s="26">
         <f ca="1">TODAY()</f>
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="12"/>
@@ -3024,6 +3127,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3161,22 +3279,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3192,21 +3312,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF02CE9-A0FC-452A-9A65-33A37A1730B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFCD04A-4CE8-4359-915C-E80DA4AF44CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="2655" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2565" yWindow="3000" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="95">
   <si>
     <t>分類</t>
   </si>
@@ -642,6 +642,107 @@
       <t>シ</t>
     </rPh>
     <rPh sb="25" eb="28">
+      <t>フグアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各敵の当たり判定デバック描画をデバックメニューに移行し各敵の当たり判定描画オンオフできるように実装</t>
+    <rPh sb="0" eb="2">
+      <t>カクテキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カクテキ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="33" eb="37">
+      <t>ハンテイビョウガ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デバックメニューのウィンドウモードをオンするとマウスカーソルが消えてしまう不具合</t>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>フグアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュジャンプタックルを行うと敵をすり抜ける不具合</t>
+    <rPh sb="13" eb="14">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>フグアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タックル攻撃を行い敵に当たったら止まるだけではなく少し後ろにノックバックする</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Acidの当たり判定が死んでも残っている不具合</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
       <t>フグアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2107,6 +2208,9 @@
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="2:8" ht="18.75">
+      <c r="B34" t="s">
+        <v>90</v>
+      </c>
       <c r="C34"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -2115,6 +2219,9 @@
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="2:8" ht="18.75">
+      <c r="B35" t="s">
+        <v>91</v>
+      </c>
       <c r="C35"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -2123,6 +2230,9 @@
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="2:8" ht="18.75">
+      <c r="B36" t="s">
+        <v>92</v>
+      </c>
       <c r="C36"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -2131,6 +2241,9 @@
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="2:8" ht="18.75">
+      <c r="B37" t="s">
+        <v>93</v>
+      </c>
       <c r="C37"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -2139,6 +2252,9 @@
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="2:8" ht="18.75">
+      <c r="B38" t="s">
+        <v>94</v>
+      </c>
       <c r="C38"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>

--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFCD04A-4CE8-4359-915C-E80DA4AF44CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC9ABF3-56EE-4B8C-9F84-44B9674E3480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="3000" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3255" yWindow="3690" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="97">
   <si>
     <t>分類</t>
   </si>
@@ -743,6 +743,47 @@
       <t>ノコ</t>
     </rPh>
     <rPh sb="20" eb="23">
+      <t>フグアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EnemyNormalのショットガン攻撃を受けた際、Hitアニメーションを使用する</t>
+    <rPh sb="18" eb="20">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル画面でデバックメニューを開いてマウス左クリックを押すとシーン遷移し進んでしまう不具合</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="43" eb="46">
       <t>フグアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2263,6 +2304,9 @@
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="2:8" ht="18.75">
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
       <c r="C39"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -2271,6 +2315,9 @@
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="2:8" ht="18.75">
+      <c r="B40" t="s">
+        <v>96</v>
+      </c>
       <c r="C40"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>

--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC9ABF3-56EE-4B8C-9F84-44B9674E3480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC07370-57B8-4850-98C6-61DEA2C2B3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3690" windowWidth="24600" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3855" yWindow="2070" windowWidth="24600" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="プルダウン用" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">集計!$B$2:$G$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="99">
   <si>
     <t>分類</t>
   </si>
@@ -603,28 +603,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>射撃タスクチュートリアルでショットガンで敵を倒した際タスクカウントが進まない不具合</t>
-    <rPh sb="0" eb="2">
-      <t>シャゲキ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>タオ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>スス</t>
-    </rPh>
-    <rPh sb="38" eb="41">
-      <t>フグアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ショットガンで倒した際吹き飛んで死なないことがある不具合</t>
     <rPh sb="7" eb="8">
       <t>タオ</t>
@@ -647,37 +625,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>各敵の当たり判定デバック描画をデバックメニューに移行し各敵の当たり判定描画オンオフできるように実装</t>
-    <rPh sb="0" eb="2">
-      <t>カクテキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ビョウガ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>イコウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>カクテキ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="33" eb="37">
-      <t>ハンテイビョウガ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>デバックメニューのウィンドウモードをオンするとマウスカーソルが消えてしまう不具合</t>
     <rPh sb="31" eb="32">
       <t>キ</t>
@@ -785,6 +732,55 @@
     </rPh>
     <rPh sb="43" eb="46">
       <t>フグアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム光らす</t>
+    <rPh sb="4" eb="5">
+      <t>ヒカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性能は同じで見た目のみ違うモデルの実装</t>
+    <rPh sb="0" eb="2">
+      <t>セイノウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テクスチャを変えたモデルの実装</t>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵AIとしてトークンシステムの実装</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1693,7 +1689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I105"/>
+  <dimension ref="B1:I104"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -2151,7 +2147,7 @@
     </row>
     <row r="25" spans="2:8" ht="18.75">
       <c r="B25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="4"/>
@@ -2162,7 +2158,7 @@
     </row>
     <row r="26" spans="2:8" ht="18.75">
       <c r="B26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C26"/>
       <c r="D26" s="4"/>
@@ -2173,52 +2169,51 @@
     </row>
     <row r="27" spans="2:8" ht="18.75">
       <c r="B27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C27"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="6"/>
+      <c r="H27" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="28" spans="2:8" ht="18.75">
       <c r="B28" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C28"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="6"/>
+      <c r="H28" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="29" spans="2:8" ht="18.75">
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
       <c r="C29"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="6"/>
+      <c r="H29" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="30" spans="2:8" ht="18.75">
-      <c r="B30" t="s">
-        <v>86</v>
-      </c>
       <c r="C30"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="6"/>
+      <c r="H30" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="31" spans="2:8" ht="18.75">
-      <c r="B31" t="s">
-        <v>87</v>
-      </c>
       <c r="C31"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -2227,9 +2222,6 @@
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="2:8" ht="18.75">
-      <c r="B32" t="s">
-        <v>88</v>
-      </c>
       <c r="C32"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -2238,9 +2230,6 @@
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="2:8" ht="18.75">
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
       <c r="C33"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -2250,7 +2239,7 @@
     </row>
     <row r="34" spans="2:8" ht="18.75">
       <c r="B34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34"/>
       <c r="D34" s="4"/>
@@ -2261,7 +2250,7 @@
     </row>
     <row r="35" spans="2:8" ht="18.75">
       <c r="B35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35"/>
       <c r="D35" s="4"/>
@@ -2272,7 +2261,7 @@
     </row>
     <row r="36" spans="2:8" ht="18.75">
       <c r="B36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C36"/>
       <c r="D36" s="4"/>
@@ -2283,7 +2272,7 @@
     </row>
     <row r="37" spans="2:8" ht="18.75">
       <c r="B37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C37"/>
       <c r="D37" s="4"/>
@@ -2294,7 +2283,7 @@
     </row>
     <row r="38" spans="2:8" ht="18.75">
       <c r="B38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38"/>
       <c r="D38" s="4"/>
@@ -2305,7 +2294,7 @@
     </row>
     <row r="39" spans="2:8" ht="18.75">
       <c r="B39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39"/>
       <c r="D39" s="4"/>
@@ -2316,7 +2305,7 @@
     </row>
     <row r="40" spans="2:8" ht="18.75">
       <c r="B40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C40"/>
       <c r="D40" s="4"/>
@@ -2326,6 +2315,9 @@
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="2:8" ht="18.75">
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
       <c r="C41"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2334,6 +2326,9 @@
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="2:8" ht="18.75">
+      <c r="B42" t="s">
+        <v>97</v>
+      </c>
       <c r="C42"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -2342,6 +2337,9 @@
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="2:8" ht="18.75">
+      <c r="B43" t="s">
+        <v>98</v>
+      </c>
       <c r="C43"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -2534,7 +2532,7 @@
       <c r="H66" s="6"/>
     </row>
     <row r="67" spans="3:8" ht="18.75">
-      <c r="C67"/>
+      <c r="C67" s="6"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
@@ -2542,7 +2540,7 @@
       <c r="H67" s="6"/>
     </row>
     <row r="68" spans="3:8" ht="18.75">
-      <c r="C68" s="6"/>
+      <c r="C68"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
@@ -2750,12 +2748,12 @@
       <c r="H93" s="6"/>
     </row>
     <row r="94" spans="3:8" ht="18.75">
-      <c r="C94"/>
-      <c r="D94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="47"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
-      <c r="H94" s="6"/>
+      <c r="H94" s="4"/>
     </row>
     <row r="95" spans="3:8" ht="18.75">
       <c r="C95" s="4"/>
@@ -2782,12 +2780,12 @@
       <c r="H97" s="4"/>
     </row>
     <row r="98" spans="3:8" ht="18.75">
-      <c r="C98" s="4"/>
-      <c r="D98" s="47"/>
+      <c r="C98"/>
+      <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
+      <c r="H98" s="6"/>
     </row>
     <row r="99" spans="3:8" ht="18.75">
       <c r="C99"/>
@@ -2798,16 +2796,16 @@
       <c r="H99" s="6"/>
     </row>
     <row r="100" spans="3:8" ht="18.75">
-      <c r="C100"/>
-      <c r="D100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="47"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
       <c r="H100" s="6"/>
     </row>
     <row r="101" spans="3:8" ht="18.75">
-      <c r="C101" s="4"/>
-      <c r="D101" s="47"/>
+      <c r="C101"/>
+      <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
@@ -2822,25 +2820,17 @@
       <c r="H102" s="6"/>
     </row>
     <row r="103" spans="3:8" ht="18.75">
-      <c r="C103"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="6"/>
+      <c r="C103" s="43"/>
+      <c r="D103" s="39"/>
+      <c r="H103" s="36"/>
     </row>
     <row r="104" spans="3:8" ht="18.75">
       <c r="C104" s="43"/>
       <c r="D104" s="39"/>
       <c r="H104" s="36"/>
     </row>
-    <row r="105" spans="3:8" ht="18.75">
-      <c r="C105" s="43"/>
-      <c r="D105" s="39"/>
-      <c r="H105" s="36"/>
-    </row>
   </sheetData>
-  <autoFilter ref="E2:G105" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E2:G104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -2851,19 +2841,19 @@
           <x14:formula1>
             <xm:f>プルダウン用!$B$3:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G99:G100 G102:G1048576 G1:G94</xm:sqref>
+          <xm:sqref>G98:G99 G101:G1048576 G1:G93</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
             <xm:f>プルダウン用!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F102:F1048576 F1:F100</xm:sqref>
+          <xm:sqref>F101:F1048576 F1:F99</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
             <xm:f>プルダウン用!$F$3:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E99:E100 E102:E1048576 E1:E94</xm:sqref>
+          <xm:sqref>E98:E99 E101:E1048576 E1:E93</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3290,21 +3280,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3442,24 +3417,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3475,4 +3448,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC07370-57B8-4850-98C6-61DEA2C2B3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EC6545-EDF6-48EE-A320-6D05F8106556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="2070" windowWidth="24600" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="975" windowWidth="24600" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="98">
   <si>
     <t>分類</t>
   </si>
@@ -672,25 +672,6 @@
     </rPh>
     <rPh sb="27" eb="28">
       <t>ウシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Acidの当たり判定が死んでも残っている不具合</t>
-    <rPh sb="5" eb="6">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ノコ</t>
-    </rPh>
-    <rPh sb="20" eb="23">
-      <t>フグアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2219,7 +2200,9 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="6"/>
+      <c r="H31" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="32" spans="2:8" ht="18.75">
       <c r="C32"/>
@@ -2227,7 +2210,9 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="6"/>
+      <c r="H32" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="33" spans="2:8" ht="18.75">
       <c r="C33"/>
@@ -2235,12 +2220,11 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="6"/>
+      <c r="H33" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="34" spans="2:8" ht="18.75">
-      <c r="B34" t="s">
-        <v>89</v>
-      </c>
       <c r="C34"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -2249,9 +2233,6 @@
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="2:8" ht="18.75">
-      <c r="B35" t="s">
-        <v>90</v>
-      </c>
       <c r="C35"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -2260,9 +2241,6 @@
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="2:8" ht="18.75">
-      <c r="B36" t="s">
-        <v>91</v>
-      </c>
       <c r="C36"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -2271,9 +2249,6 @@
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="2:8" ht="18.75">
-      <c r="B37" t="s">
-        <v>92</v>
-      </c>
       <c r="C37"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -2283,7 +2258,7 @@
     </row>
     <row r="38" spans="2:8" ht="18.75">
       <c r="B38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C38"/>
       <c r="D38" s="4"/>
@@ -2294,7 +2269,7 @@
     </row>
     <row r="39" spans="2:8" ht="18.75">
       <c r="B39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C39"/>
       <c r="D39" s="4"/>
@@ -2305,7 +2280,7 @@
     </row>
     <row r="40" spans="2:8" ht="18.75">
       <c r="B40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C40"/>
       <c r="D40" s="4"/>
@@ -2316,7 +2291,7 @@
     </row>
     <row r="41" spans="2:8" ht="18.75">
       <c r="B41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C41"/>
       <c r="D41" s="4"/>
@@ -2327,7 +2302,7 @@
     </row>
     <row r="42" spans="2:8" ht="18.75">
       <c r="B42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C42"/>
       <c r="D42" s="4"/>
@@ -2338,7 +2313,7 @@
     </row>
     <row r="43" spans="2:8" ht="18.75">
       <c r="B43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C43"/>
       <c r="D43" s="4"/>
@@ -3280,6 +3255,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3417,22 +3407,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3448,21 +3440,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EC6545-EDF6-48EE-A320-6D05F8106556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09ED3D0-3550-4832-9528-277846D0BAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2685" yWindow="975" windowWidth="24600" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="97">
   <si>
     <t>分類</t>
   </si>
@@ -583,22 +583,6 @@
     </rPh>
     <rPh sb="31" eb="33">
       <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面サイズを変更した際のリザルトシーンUI調整</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>チョウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1174,7 +1158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1328,6 +1312,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1988,7 +1978,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="18.75">
+    <row r="17" spans="2:9" ht="18.75">
       <c r="B17" s="33" t="s">
         <v>43</v>
       </c>
@@ -2007,7 +1997,7 @@
       </c>
       <c r="H17" s="42"/>
     </row>
-    <row r="18" spans="2:8" ht="18.75">
+    <row r="18" spans="2:9" ht="18.75">
       <c r="B18" s="34" t="s">
         <v>42</v>
       </c>
@@ -2025,7 +2015,7 @@
       </c>
       <c r="H18" s="36"/>
     </row>
-    <row r="19" spans="2:8" ht="18.75">
+    <row r="19" spans="2:9" ht="18.75">
       <c r="B19" s="34" t="s">
         <v>42</v>
       </c>
@@ -2045,7 +2035,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="19.5" thickBot="1">
+    <row r="20" spans="2:9" ht="19.5" thickBot="1">
       <c r="B20" s="35"/>
       <c r="C20" s="44"/>
       <c r="D20" s="40"/>
@@ -2056,7 +2046,7 @@
       </c>
       <c r="H20" s="37"/>
     </row>
-    <row r="21" spans="2:8" ht="19.5" thickBot="1">
+    <row r="21" spans="2:9" ht="19.5" thickBot="1">
       <c r="B21" s="48" t="s">
         <v>50</v>
       </c>
@@ -2075,7 +2065,7 @@
       </c>
       <c r="H21" s="51"/>
     </row>
-    <row r="22" spans="2:8" ht="19.5" thickBot="1">
+    <row r="22" spans="2:9" ht="19.5" thickBot="1">
       <c r="B22" s="48" t="s">
         <v>74</v>
       </c>
@@ -2096,7 +2086,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="19.5" thickBot="1">
+    <row r="23" spans="2:9" ht="19.5" thickBot="1">
       <c r="B23" s="48" t="s">
         <v>64</v>
       </c>
@@ -2111,7 +2101,7 @@
       </c>
       <c r="H23" s="52"/>
     </row>
-    <row r="24" spans="2:8" ht="19.5" thickBot="1">
+    <row r="24" spans="2:9" ht="19.5" thickBot="1">
       <c r="B24" s="49" t="s">
         <v>65</v>
       </c>
@@ -2126,7 +2116,7 @@
       </c>
       <c r="H24" s="52"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:9" ht="18.75">
       <c r="B25" t="s">
         <v>78</v>
       </c>
@@ -2137,7 +2127,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="2:8" ht="18.75">
+    <row r="26" spans="2:9" ht="18.75">
       <c r="B26" t="s">
         <v>82</v>
       </c>
@@ -2148,7 +2138,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="2:8" ht="18.75">
+    <row r="27" spans="2:9" ht="18.75">
       <c r="B27" t="s">
         <v>81</v>
       </c>
@@ -2156,109 +2146,133 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" t="s">
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="55"/>
+    </row>
+    <row r="28" spans="2:9" ht="18.75">
+      <c r="B28" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="18.75">
-      <c r="B28" t="s">
-        <v>87</v>
       </c>
       <c r="C28"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" t="s">
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="55"/>
+    </row>
+    <row r="29" spans="2:9" ht="18.75">
+      <c r="B29" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" ht="18.75">
       <c r="C29"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="18.75">
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="55"/>
+    </row>
+    <row r="30" spans="2:9" ht="18.75">
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
       <c r="C30"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="18.75">
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="55"/>
+    </row>
+    <row r="31" spans="2:9" ht="18.75">
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
       <c r="C31"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="18.75">
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="55"/>
+    </row>
+    <row r="32" spans="2:9" ht="18.75">
+      <c r="B32" t="s">
+        <v>90</v>
+      </c>
       <c r="C32"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" ht="18.75">
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="55"/>
+    </row>
+    <row r="33" spans="2:9" ht="18.75">
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
       <c r="C33"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" t="s">
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="55"/>
+    </row>
+    <row r="34" spans="2:9" ht="18.75">
+      <c r="B34" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="34" spans="2:8" ht="18.75">
       <c r="C34"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="35" spans="2:8" ht="18.75">
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="55"/>
+    </row>
+    <row r="35" spans="2:9" ht="18.75">
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
       <c r="C35"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" spans="2:8" ht="18.75">
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="55"/>
+    </row>
+    <row r="36" spans="2:9" ht="18.75">
+      <c r="B36" t="s">
+        <v>93</v>
+      </c>
       <c r="C36"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" spans="2:8" ht="18.75">
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+    </row>
+    <row r="37" spans="2:9" ht="18.75">
+      <c r="B37" t="s">
+        <v>94</v>
+      </c>
       <c r="C37"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" spans="2:8" ht="18.75">
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+    </row>
+    <row r="38" spans="2:9" ht="18.75">
       <c r="B38" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C38"/>
       <c r="D38" s="4"/>
@@ -2267,9 +2281,9 @@
       <c r="G38" s="4"/>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="2:8" ht="18.75">
+    <row r="39" spans="2:9" ht="18.75">
       <c r="B39" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C39"/>
       <c r="D39" s="4"/>
@@ -2278,9 +2292,9 @@
       <c r="G39" s="4"/>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="2:8" ht="18.75">
+    <row r="40" spans="2:9" ht="18.75">
       <c r="B40" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C40"/>
       <c r="D40" s="4"/>
@@ -2289,10 +2303,7 @@
       <c r="G40" s="4"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="2:8" ht="18.75">
-      <c r="B41" t="s">
-        <v>95</v>
-      </c>
+    <row r="41" spans="2:9" ht="18.75">
       <c r="C41"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2300,10 +2311,7 @@
       <c r="G41" s="4"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8" ht="18.75">
-      <c r="B42" t="s">
-        <v>96</v>
-      </c>
+    <row r="42" spans="2:9" ht="18.75">
       <c r="C42"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -2311,10 +2319,7 @@
       <c r="G42" s="4"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="2:8" ht="18.75">
-      <c r="B43" t="s">
-        <v>97</v>
-      </c>
+    <row r="43" spans="2:9" ht="18.75">
       <c r="C43"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -2322,7 +2327,7 @@
       <c r="G43" s="4"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="2:8" ht="18.75">
+    <row r="44" spans="2:9" ht="18.75">
       <c r="C44"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -2330,7 +2335,7 @@
       <c r="G44" s="4"/>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="2:8" ht="18.75">
+    <row r="45" spans="2:9" ht="18.75">
       <c r="C45"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -2338,7 +2343,7 @@
       <c r="G45" s="4"/>
       <c r="H45" s="6"/>
     </row>
-    <row r="46" spans="2:8" ht="18.75">
+    <row r="46" spans="2:9" ht="18.75">
       <c r="C46"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -2346,7 +2351,7 @@
       <c r="G46" s="4"/>
       <c r="H46" s="6"/>
     </row>
-    <row r="47" spans="2:8" ht="18.75">
+    <row r="47" spans="2:9" ht="18.75">
       <c r="C47"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -2354,7 +2359,7 @@
       <c r="G47" s="4"/>
       <c r="H47" s="6"/>
     </row>
-    <row r="48" spans="2:8" ht="18.75">
+    <row r="48" spans="2:9" ht="18.75">
       <c r="C48"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3255,21 +3260,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3407,24 +3397,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3440,4 +3428,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sho24\OneDrive\ドキュメント\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09ED3D0-3550-4832-9528-277846D0BAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCC3D19-6748-4589-954C-4F8065D38679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="975" windowWidth="24600" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3435" yWindow="3645" windowWidth="21420" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="98">
   <si>
     <t>分類</t>
   </si>
@@ -746,6 +746,22 @@
     </rPh>
     <rPh sb="15" eb="17">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無名名前空間と名前付き名前空間の違い</t>
+    <rPh sb="0" eb="6">
+      <t>ムメイナマエクウカン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ナマエツ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ナマエクウカン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>チガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1158,7 +1174,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1312,12 +1328,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1978,7 +1988,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="18.75">
+    <row r="17" spans="2:8" ht="18.75">
       <c r="B17" s="33" t="s">
         <v>43</v>
       </c>
@@ -1997,7 +2007,7 @@
       </c>
       <c r="H17" s="42"/>
     </row>
-    <row r="18" spans="2:9" ht="18.75">
+    <row r="18" spans="2:8" ht="18.75">
       <c r="B18" s="34" t="s">
         <v>42</v>
       </c>
@@ -2015,7 +2025,7 @@
       </c>
       <c r="H18" s="36"/>
     </row>
-    <row r="19" spans="2:9" ht="18.75">
+    <row r="19" spans="2:8" ht="18.75">
       <c r="B19" s="34" t="s">
         <v>42</v>
       </c>
@@ -2035,7 +2045,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="19.5" thickBot="1">
+    <row r="20" spans="2:8" ht="19.5" thickBot="1">
       <c r="B20" s="35"/>
       <c r="C20" s="44"/>
       <c r="D20" s="40"/>
@@ -2046,7 +2056,7 @@
       </c>
       <c r="H20" s="37"/>
     </row>
-    <row r="21" spans="2:9" ht="19.5" thickBot="1">
+    <row r="21" spans="2:8" ht="19.5" thickBot="1">
       <c r="B21" s="48" t="s">
         <v>50</v>
       </c>
@@ -2065,7 +2075,7 @@
       </c>
       <c r="H21" s="51"/>
     </row>
-    <row r="22" spans="2:9" ht="19.5" thickBot="1">
+    <row r="22" spans="2:8" ht="19.5" thickBot="1">
       <c r="B22" s="48" t="s">
         <v>74</v>
       </c>
@@ -2086,7 +2096,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="19.5" thickBot="1">
+    <row r="23" spans="2:8" ht="19.5" thickBot="1">
       <c r="B23" s="48" t="s">
         <v>64</v>
       </c>
@@ -2101,7 +2111,7 @@
       </c>
       <c r="H23" s="52"/>
     </row>
-    <row r="24" spans="2:9" ht="19.5" thickBot="1">
+    <row r="24" spans="2:8" ht="19.5" thickBot="1">
       <c r="B24" s="49" t="s">
         <v>65</v>
       </c>
@@ -2116,7 +2126,7 @@
       </c>
       <c r="H24" s="52"/>
     </row>
-    <row r="25" spans="2:9" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75">
       <c r="B25" t="s">
         <v>78</v>
       </c>
@@ -2127,7 +2137,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="2:9" ht="18.75">
+    <row r="26" spans="2:8" ht="18.75">
       <c r="B26" t="s">
         <v>82</v>
       </c>
@@ -2138,7 +2148,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="2:9" ht="18.75">
+    <row r="27" spans="2:8" ht="18.75">
       <c r="B27" t="s">
         <v>81</v>
       </c>
@@ -2146,11 +2156,10 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="55"/>
-    </row>
-    <row r="28" spans="2:9" ht="18.75">
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="2:8" ht="18.75">
       <c r="B28" t="s">
         <v>80</v>
       </c>
@@ -2158,11 +2167,10 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="55"/>
-    </row>
-    <row r="29" spans="2:9" ht="18.75">
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="2:8" ht="18.75">
       <c r="B29" t="s">
         <v>79</v>
       </c>
@@ -2170,11 +2178,10 @@
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="55"/>
-    </row>
-    <row r="30" spans="2:9" ht="18.75">
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="2:8" ht="18.75">
       <c r="B30" t="s">
         <v>88</v>
       </c>
@@ -2182,11 +2189,10 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="55"/>
-    </row>
-    <row r="31" spans="2:9" ht="18.75">
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="2:8" ht="18.75">
       <c r="B31" t="s">
         <v>89</v>
       </c>
@@ -2194,11 +2200,10 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="55"/>
-    </row>
-    <row r="32" spans="2:9" ht="18.75">
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="2:8" ht="18.75">
       <c r="B32" t="s">
         <v>90</v>
       </c>
@@ -2206,11 +2211,10 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="55"/>
-    </row>
-    <row r="33" spans="2:9" ht="18.75">
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="2:8" ht="18.75">
       <c r="B33" t="s">
         <v>92</v>
       </c>
@@ -2218,11 +2222,10 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55"/>
-    </row>
-    <row r="34" spans="2:9" ht="18.75">
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="2:8" ht="18.75">
       <c r="B34" t="s">
         <v>91</v>
       </c>
@@ -2230,11 +2233,10 @@
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="55"/>
-    </row>
-    <row r="35" spans="2:9" ht="18.75">
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="2:8" ht="18.75">
       <c r="B35" t="s">
         <v>87</v>
       </c>
@@ -2242,11 +2244,10 @@
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="55"/>
-    </row>
-    <row r="36" spans="2:9" ht="18.75">
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="2:8" ht="18.75">
       <c r="B36" t="s">
         <v>93</v>
       </c>
@@ -2254,11 +2255,10 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-    </row>
-    <row r="37" spans="2:9" ht="18.75">
+      <c r="G36" s="4"/>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="2:8" ht="18.75">
       <c r="B37" t="s">
         <v>94</v>
       </c>
@@ -2266,11 +2266,10 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-    </row>
-    <row r="38" spans="2:9" ht="18.75">
+      <c r="G37" s="4"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="2:8" ht="18.75">
       <c r="B38" t="s">
         <v>95</v>
       </c>
@@ -2281,7 +2280,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="2:9" ht="18.75">
+    <row r="39" spans="2:8" ht="18.75">
       <c r="B39" t="s">
         <v>96</v>
       </c>
@@ -2292,7 +2291,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="2:9" ht="18.75">
+    <row r="40" spans="2:8" ht="18.75">
       <c r="B40" t="s">
         <v>86</v>
       </c>
@@ -2303,7 +2302,10 @@
       <c r="G40" s="4"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="2:9" ht="18.75">
+    <row r="41" spans="2:8" ht="18.75">
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
       <c r="C41"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2311,7 +2313,7 @@
       <c r="G41" s="4"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:9" ht="18.75">
+    <row r="42" spans="2:8" ht="18.75">
       <c r="C42"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -2319,7 +2321,7 @@
       <c r="G42" s="4"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="2:9" ht="18.75">
+    <row r="43" spans="2:8" ht="18.75">
       <c r="C43"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -2327,7 +2329,7 @@
       <c r="G43" s="4"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="2:9" ht="18.75">
+    <row r="44" spans="2:8" ht="18.75">
       <c r="C44"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -2335,7 +2337,7 @@
       <c r="G44" s="4"/>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="2:9" ht="18.75">
+    <row r="45" spans="2:8" ht="18.75">
       <c r="C45"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -2343,7 +2345,7 @@
       <c r="G45" s="4"/>
       <c r="H45" s="6"/>
     </row>
-    <row r="46" spans="2:9" ht="18.75">
+    <row r="46" spans="2:8" ht="18.75">
       <c r="C46"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -2351,7 +2353,7 @@
       <c r="G46" s="4"/>
       <c r="H46" s="6"/>
     </row>
-    <row r="47" spans="2:9" ht="18.75">
+    <row r="47" spans="2:8" ht="18.75">
       <c r="C47"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -2359,7 +2361,7 @@
       <c r="G47" s="4"/>
       <c r="H47" s="6"/>
     </row>
-    <row r="48" spans="2:9" ht="18.75">
+    <row r="48" spans="2:8" ht="18.75">
       <c r="C48"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3260,6 +3262,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3397,22 +3414,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3428,21 +3447,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sho24\OneDrive\ドキュメント\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCC3D19-6748-4589-954C-4F8065D38679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D69D595-4A4E-4176-93A8-B4F704EE6B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3435" yWindow="3645" windowWidth="21420" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="プルダウン用" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">集計!$B$2:$G$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="97">
   <si>
     <t>分類</t>
   </si>
@@ -489,25 +489,6 @@
       <t>ウゴ</t>
     </rPh>
     <rPh sb="42" eb="45">
-      <t>フグアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タックル攻撃を行うと敵をすり抜けてしまう不具合</t>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="20" eb="23">
       <t>フグアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1670,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I104"/>
+  <dimension ref="B1:I103"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -1777,10 +1758,10 @@
     </row>
     <row r="6" spans="2:8" ht="18.75">
       <c r="B6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="36" t="s">
         <v>83</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>84</v>
       </c>
       <c r="D6" s="39">
         <v>0.5</v>
@@ -1795,10 +1776,10 @@
     </row>
     <row r="7" spans="2:8" ht="18.75">
       <c r="B7" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" s="39">
         <v>1</v>
@@ -2139,7 +2120,7 @@
     </row>
     <row r="26" spans="2:8" ht="18.75">
       <c r="B26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26"/>
       <c r="D26" s="4"/>
@@ -2150,7 +2131,7 @@
     </row>
     <row r="27" spans="2:8" ht="18.75">
       <c r="B27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27"/>
       <c r="D27" s="4"/>
@@ -2161,7 +2142,7 @@
     </row>
     <row r="28" spans="2:8" ht="18.75">
       <c r="B28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28"/>
       <c r="D28" s="4"/>
@@ -2172,7 +2153,7 @@
     </row>
     <row r="29" spans="2:8" ht="18.75">
       <c r="B29" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C29"/>
       <c r="D29" s="4"/>
@@ -2205,7 +2186,7 @@
     </row>
     <row r="32" spans="2:8" ht="18.75">
       <c r="B32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C32"/>
       <c r="D32" s="4"/>
@@ -2216,7 +2197,7 @@
     </row>
     <row r="33" spans="2:8" ht="18.75">
       <c r="B33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C33"/>
       <c r="D33" s="4"/>
@@ -2227,7 +2208,7 @@
     </row>
     <row r="34" spans="2:8" ht="18.75">
       <c r="B34" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C34"/>
       <c r="D34" s="4"/>
@@ -2238,14 +2219,14 @@
     </row>
     <row r="35" spans="2:8" ht="18.75">
       <c r="B35" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C35"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="H35" s="6"/>
     </row>
     <row r="36" spans="2:8" ht="18.75">
       <c r="B36" t="s">
@@ -2282,7 +2263,7 @@
     </row>
     <row r="39" spans="2:8" ht="18.75">
       <c r="B39" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C39"/>
       <c r="D39" s="4"/>
@@ -2293,7 +2274,7 @@
     </row>
     <row r="40" spans="2:8" ht="18.75">
       <c r="B40" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C40"/>
       <c r="D40" s="4"/>
@@ -2303,9 +2284,6 @@
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="2:8" ht="18.75">
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
       <c r="C41"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2506,7 +2484,7 @@
       <c r="H65" s="6"/>
     </row>
     <row r="66" spans="3:8" ht="18.75">
-      <c r="C66"/>
+      <c r="C66" s="6"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
@@ -2514,7 +2492,7 @@
       <c r="H66" s="6"/>
     </row>
     <row r="67" spans="3:8" ht="18.75">
-      <c r="C67" s="6"/>
+      <c r="C67"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
@@ -2722,12 +2700,12 @@
       <c r="H92" s="6"/>
     </row>
     <row r="93" spans="3:8" ht="18.75">
-      <c r="C93"/>
-      <c r="D93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="47"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
-      <c r="H93" s="6"/>
+      <c r="H93" s="4"/>
     </row>
     <row r="94" spans="3:8" ht="18.75">
       <c r="C94" s="4"/>
@@ -2754,12 +2732,12 @@
       <c r="H96" s="4"/>
     </row>
     <row r="97" spans="3:8" ht="18.75">
-      <c r="C97" s="4"/>
-      <c r="D97" s="47"/>
+      <c r="C97"/>
+      <c r="D97" s="4"/>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
+      <c r="H97" s="6"/>
     </row>
     <row r="98" spans="3:8" ht="18.75">
       <c r="C98"/>
@@ -2770,16 +2748,16 @@
       <c r="H98" s="6"/>
     </row>
     <row r="99" spans="3:8" ht="18.75">
-      <c r="C99"/>
-      <c r="D99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="47"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
       <c r="H99" s="6"/>
     </row>
     <row r="100" spans="3:8" ht="18.75">
-      <c r="C100" s="4"/>
-      <c r="D100" s="47"/>
+      <c r="C100"/>
+      <c r="D100" s="4"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
@@ -2794,25 +2772,17 @@
       <c r="H101" s="6"/>
     </row>
     <row r="102" spans="3:8" ht="18.75">
-      <c r="C102"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="6"/>
+      <c r="C102" s="43"/>
+      <c r="D102" s="39"/>
+      <c r="H102" s="36"/>
     </row>
     <row r="103" spans="3:8" ht="18.75">
       <c r="C103" s="43"/>
       <c r="D103" s="39"/>
       <c r="H103" s="36"/>
     </row>
-    <row r="104" spans="3:8" ht="18.75">
-      <c r="C104" s="43"/>
-      <c r="D104" s="39"/>
-      <c r="H104" s="36"/>
-    </row>
   </sheetData>
-  <autoFilter ref="E2:G104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E2:G103" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -2823,19 +2793,19 @@
           <x14:formula1>
             <xm:f>プルダウン用!$B$3:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G98:G99 G101:G1048576 G1:G93</xm:sqref>
+          <xm:sqref>G97:G98 G100:G1048576 G1:G92</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
             <xm:f>プルダウン用!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F101:F1048576 F1:F99</xm:sqref>
+          <xm:sqref>F100:F1048576 F1:F98</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
             <xm:f>プルダウン用!$F$3:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E98:E99 E101:E1048576 E1:E93</xm:sqref>
+          <xm:sqref>E97:E98 E100:E1048576 E1:E92</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3262,21 +3232,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3414,24 +3369,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3447,4 +3400,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sho24\OneDrive\ドキュメント\MyGame3D2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D69D595-4A4E-4176-93A8-B4F704EE6B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B40FB5-EAF0-4051-81E9-B8CE8D8A0EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3435" yWindow="3645" windowWidth="21420" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1335" windowWidth="24600" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -1712,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="36" t="s">
         <v>73</v>
@@ -2870,11 +2870,11 @@
       </c>
       <c r="D3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "完了")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "作業中")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
@@ -2882,14 +2882,14 @@
       </c>
       <c r="G3" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
-        <v>0</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="13">
         <f>SUMIF(コスト表!G:G,"完了",コスト表!D:D)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>18</v>
@@ -2925,11 +2925,11 @@
       </c>
       <c r="J4" s="13">
         <f ca="1">NETWORKDAYS(J5,J6)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="13">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M4" s="12"/>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="J6" s="26">
         <f ca="1">TODAY()</f>
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="12"/>
@@ -3094,7 +3094,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="24">
         <f>ROUNDDOWN(COUNTIF(コスト表!G:G, "完了") / COUNTA(コスト表!G:G) * 100,1)</f>
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -3232,6 +3232,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3369,22 +3384,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3400,21 +3417,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B40FB5-EAF0-4051-81E9-B8CE8D8A0EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356D65C3-0F4A-4EE5-B4AD-E3DFADB5940A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="1335" windowWidth="24600" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2025" yWindow="3900" windowWidth="13515" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F21" s="50"/>
       <c r="G21" s="50" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H21" s="51"/>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="J3" s="13">
         <f>SUMIF(コスト表!G:G,"完了",コスト表!D:D)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>18</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="K4" s="13">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M4" s="12"/>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="D6" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ステージ", コスト表!G:G, "完了")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ステージ", コスト表!G:G, "作業中")</f>
@@ -2986,11 +2986,11 @@
       </c>
       <c r="F6" s="28">
         <f>SUMIFS(コスト表!D:D,コスト表!B:B,"ステージ",コスト表!G:G,"未着手")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "ステージ", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "ステージ") * 100,1)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6" s="18" t="s">
         <v>21</v>
@@ -3094,7 +3094,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="24">
         <f>ROUNDDOWN(COUNTIF(コスト表!G:G, "完了") / COUNTA(コスト表!G:G) * 100,1)</f>
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -3232,21 +3232,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3384,24 +3369,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3417,4 +3400,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356D65C3-0F4A-4EE5-B4AD-E3DFADB5940A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E111C7F-93A6-4D52-BAA6-6BE1108B1936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="3900" windowWidth="13515" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4035" yWindow="3570" windowWidth="22950" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -1770,7 +1770,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H6" s="36"/>
     </row>
@@ -1788,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H7" s="36"/>
     </row>
@@ -2870,26 +2870,26 @@
       </c>
       <c r="D3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "完了")</f>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "作業中")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="G3" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
-        <v>16.600000000000001</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="13">
         <f>SUMIF(コスト表!G:G,"完了",コスト表!D:D)</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>18</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="K4" s="13">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M4" s="12"/>
     </row>
@@ -3094,7 +3094,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="24">
         <f>ROUNDDOWN(COUNTIF(コスト表!G:G, "完了") / COUNTA(コスト表!G:G) * 100,1)</f>
-        <v>8.6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -3232,6 +3232,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3369,22 +3384,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3400,21 +3417,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E111C7F-93A6-4D52-BAA6-6BE1108B1936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A05BE8-6F23-4C11-8251-1F79CC90D9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4035" yWindow="3570" windowWidth="22950" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="98">
   <si>
     <t>分類</t>
   </si>
@@ -743,6 +743,25 @@
     </rPh>
     <rPh sb="16" eb="17">
       <t>チガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプション追加（自動武器切り替えオンオフ機能）</t>
+    <rPh sb="5" eb="7">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ブキキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キノウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1788,7 +1807,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7" s="36"/>
     </row>
@@ -2284,6 +2303,9 @@
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="2:8" ht="18.75">
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
       <c r="C41"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2870,11 +2892,11 @@
       </c>
       <c r="D3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "完了")</f>
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "作業中")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
@@ -2882,14 +2904,14 @@
       </c>
       <c r="G3" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
-        <v>33.299999999999997</v>
+        <v>50</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="13">
         <f>SUMIF(コスト表!G:G,"完了",コスト表!D:D)</f>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>18</v>
@@ -2929,7 +2951,7 @@
       </c>
       <c r="K4" s="13">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M4" s="12"/>
     </row>
@@ -3094,7 +3116,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="24">
         <f>ROUNDDOWN(COUNTIF(コスト表!G:G, "完了") / COUNTA(コスト表!G:G) * 100,1)</f>
-        <v>13</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -3232,21 +3254,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3384,24 +3391,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3417,4 +3422,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A05BE8-6F23-4C11-8251-1F79CC90D9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D0341C-3128-42B8-AC4E-2838B110492D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4035" yWindow="3570" windowWidth="22950" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="1065" windowWidth="22950" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -1751,7 +1751,7 @@
         <v>13</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H4" s="36"/>
     </row>
@@ -1923,7 +1923,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H13" s="43" t="s">
         <v>59</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="F17" s="38"/>
       <c r="G17" s="38" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H17" s="42"/>
     </row>
@@ -2896,11 +2896,11 @@
       </c>
       <c r="E3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "作業中")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G3" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
@@ -2932,11 +2932,11 @@
       </c>
       <c r="E4" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "作業中")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "未着手")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵") * 100,1)</f>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="J4" s="13">
         <f ca="1">NETWORKDAYS(J5,J6)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" s="13">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M4" s="12"/>
     </row>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="E5" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "Boss", コスト表!G:G, "作業中")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "Boss", コスト表!G:G, "未着手")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "Boss", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "Boss") * 100,1)</f>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="J6" s="26">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="12"/>
@@ -3254,6 +3254,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3391,22 +3406,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3422,21 +3439,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D0341C-3128-42B8-AC4E-2838B110492D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31813F5F-538F-4FAF-8960-987250B3F39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="1065" windowWidth="22950" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="プルダウン用" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">集計!$B$2:$G$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="97">
   <si>
     <t>分類</t>
   </si>
@@ -727,22 +727,6 @@
     </rPh>
     <rPh sb="15" eb="17">
       <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>無名名前空間と名前付き名前空間の違い</t>
-    <rPh sb="0" eb="6">
-      <t>ムメイナマエクウカン</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ナマエツ</t>
-    </rPh>
-    <rPh sb="11" eb="15">
-      <t>ナマエクウカン</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>チガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1670,7 +1654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I103"/>
+  <dimension ref="B1:I102"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -1751,7 +1735,7 @@
         <v>13</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="36"/>
     </row>
@@ -1769,7 +1753,7 @@
         <v>13</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H5" s="36" t="s">
         <v>49</v>
@@ -1847,7 +1831,7 @@
       </c>
       <c r="F9" s="38"/>
       <c r="G9" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H9" s="42"/>
     </row>
@@ -1865,7 +1849,7 @@
         <v>8</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H10" s="36"/>
     </row>
@@ -1883,7 +1867,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H11" s="36" t="s">
         <v>61</v>
@@ -1963,7 +1947,7 @@
         <v>8</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H15" s="43"/>
     </row>
@@ -2003,7 +1987,7 @@
       </c>
       <c r="F17" s="38"/>
       <c r="G17" s="38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="42"/>
     </row>
@@ -2021,7 +2005,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H18" s="36"/>
     </row>
@@ -2039,7 +2023,7 @@
         <v>13</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H19" s="36" t="s">
         <v>62</v>
@@ -2051,9 +2035,7 @@
       <c r="D20" s="40"/>
       <c r="E20" s="40"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="40" t="s">
-        <v>9</v>
-      </c>
+      <c r="G20" s="40"/>
       <c r="H20" s="37"/>
     </row>
     <row r="21" spans="2:8" ht="19.5" thickBot="1">
@@ -2090,7 +2072,7 @@
       </c>
       <c r="F22" s="50"/>
       <c r="G22" s="50" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H22" s="51" t="s">
         <v>76</v>
@@ -2303,9 +2285,6 @@
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="2:8" ht="18.75">
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
       <c r="C41"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2498,7 +2477,7 @@
       <c r="H64" s="6"/>
     </row>
     <row r="65" spans="3:8" ht="18.75">
-      <c r="C65"/>
+      <c r="C65" s="6"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
@@ -2506,7 +2485,7 @@
       <c r="H65" s="6"/>
     </row>
     <row r="66" spans="3:8" ht="18.75">
-      <c r="C66" s="6"/>
+      <c r="C66"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
@@ -2714,12 +2693,12 @@
       <c r="H91" s="6"/>
     </row>
     <row r="92" spans="3:8" ht="18.75">
-      <c r="C92"/>
-      <c r="D92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="47"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
-      <c r="H92" s="6"/>
+      <c r="H92" s="4"/>
     </row>
     <row r="93" spans="3:8" ht="18.75">
       <c r="C93" s="4"/>
@@ -2746,12 +2725,12 @@
       <c r="H95" s="4"/>
     </row>
     <row r="96" spans="3:8" ht="18.75">
-      <c r="C96" s="4"/>
-      <c r="D96" s="47"/>
+      <c r="C96"/>
+      <c r="D96" s="4"/>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
+      <c r="H96" s="6"/>
     </row>
     <row r="97" spans="3:8" ht="18.75">
       <c r="C97"/>
@@ -2762,16 +2741,16 @@
       <c r="H97" s="6"/>
     </row>
     <row r="98" spans="3:8" ht="18.75">
-      <c r="C98"/>
-      <c r="D98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="47"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
       <c r="H98" s="6"/>
     </row>
     <row r="99" spans="3:8" ht="18.75">
-      <c r="C99" s="4"/>
-      <c r="D99" s="47"/>
+      <c r="C99"/>
+      <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
@@ -2786,25 +2765,17 @@
       <c r="H100" s="6"/>
     </row>
     <row r="101" spans="3:8" ht="18.75">
-      <c r="C101"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="6"/>
+      <c r="C101" s="43"/>
+      <c r="D101" s="39"/>
+      <c r="H101" s="36"/>
     </row>
     <row r="102" spans="3:8" ht="18.75">
       <c r="C102" s="43"/>
       <c r="D102" s="39"/>
       <c r="H102" s="36"/>
     </row>
-    <row r="103" spans="3:8" ht="18.75">
-      <c r="C103" s="43"/>
-      <c r="D103" s="39"/>
-      <c r="H103" s="36"/>
-    </row>
   </sheetData>
-  <autoFilter ref="E2:G103" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E2:G102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -2815,19 +2786,19 @@
           <x14:formula1>
             <xm:f>プルダウン用!$B$3:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G97:G98 G100:G1048576 G1:G92</xm:sqref>
+          <xm:sqref>G96:G97 G99:G1048576 G1:G91</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
             <xm:f>プルダウン用!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F100:F1048576 F1:F98</xm:sqref>
+          <xm:sqref>F99:F1048576 F1:F97</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
             <xm:f>プルダウン用!$F$3:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E97:E98 E100:E1048576 E1:E92</xm:sqref>
+          <xm:sqref>E96:E97 E99:E1048576 E1:E91</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2892,26 +2863,26 @@
       </c>
       <c r="D3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "完了")</f>
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="E3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "作業中")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="13">
         <f>SUMIF(コスト表!G:G,"完了",コスト表!D:D)</f>
-        <v>3.5</v>
+        <v>14.5</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>18</v>
@@ -2928,7 +2899,7 @@
       </c>
       <c r="D4" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "完了")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "作業中")</f>
@@ -2936,22 +2907,22 @@
       </c>
       <c r="F4" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "未着手")</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G4" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵") * 100,1)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I4" s="16" t="s">
         <v>19</v>
       </c>
       <c r="J4" s="13">
         <f ca="1">NETWORKDAYS(J5,J6)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="13">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="M4" s="12"/>
     </row>
@@ -2965,19 +2936,19 @@
       </c>
       <c r="D5" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "Boss", コスト表!G:G, "完了")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "Boss", コスト表!G:G, "作業中")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "Boss", コスト表!G:G, "未着手")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "Boss", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "Boss") * 100,1)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>20</v>
@@ -3019,7 +2990,7 @@
       </c>
       <c r="J6" s="26">
         <f ca="1">TODAY()</f>
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="12"/>
@@ -3035,7 +3006,7 @@
       </c>
       <c r="D7" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "チュートリアル", コスト表!G:G, "完了")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "チュートリアル", コスト表!G:G, "作業中")</f>
@@ -3043,11 +3014,11 @@
       </c>
       <c r="F7" s="28">
         <f>SUMIFS(コスト表!D:D,コスト表!B:B,"チュートリアル",コスト表!G:G,"未着手")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "チュートリアル", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "チュートリアル") * 100,1)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7" s="53"/>
       <c r="J7" s="26"/>
@@ -3116,7 +3087,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="24">
         <f>ROUNDDOWN(COUNTIF(コスト表!G:G, "完了") / COUNTA(コスト表!G:G) * 100,1)</f>
-        <v>17.3</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="13" spans="2:13">

--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31813F5F-538F-4FAF-8960-987250B3F39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB5C4D7-D386-4D57-A2C8-4C67C79646A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="1065" windowWidth="22950" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="プルダウン用" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">集計!$B$2:$G$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="94">
   <si>
     <t>分類</t>
   </si>
@@ -568,75 +568,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ショットガンで倒した際吹き飛んで死なないことがある不具合</t>
-    <rPh sb="7" eb="8">
-      <t>タオ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="25" eb="28">
-      <t>フグアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>デバックメニューのウィンドウモードをオンするとマウスカーソルが消えてしまう不具合</t>
     <rPh sb="31" eb="32">
       <t>キ</t>
     </rPh>
     <rPh sb="37" eb="40">
       <t>フグアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダッシュジャンプタックルを行うと敵をすり抜ける不具合</t>
-    <rPh sb="13" eb="14">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="23" eb="26">
-      <t>フグアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タックル攻撃を行い敵に当たったら止まるだけではなく少し後ろにノックバックする</t>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ウシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1654,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I102"/>
+  <dimension ref="B1:I99"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -2154,7 +2091,7 @@
     </row>
     <row r="29" spans="2:8" ht="18.75">
       <c r="B29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29"/>
       <c r="D29" s="4"/>
@@ -2176,7 +2113,7 @@
     </row>
     <row r="31" spans="2:8" ht="18.75">
       <c r="B31" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C31"/>
       <c r="D31" s="4"/>
@@ -2187,14 +2124,14 @@
     </row>
     <row r="32" spans="2:8" ht="18.75">
       <c r="B32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C32"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="2:8" ht="18.75">
       <c r="B33" t="s">
@@ -2205,18 +2142,18 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34" spans="2:8" ht="18.75">
       <c r="B34" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C34"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="H34" s="6"/>
     </row>
     <row r="35" spans="2:8" ht="18.75">
       <c r="B35" t="s">
@@ -2231,7 +2168,7 @@
     </row>
     <row r="36" spans="2:8" ht="18.75">
       <c r="B36" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C36"/>
       <c r="D36" s="4"/>
@@ -2242,7 +2179,7 @@
     </row>
     <row r="37" spans="2:8" ht="18.75">
       <c r="B37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37"/>
       <c r="D37" s="4"/>
@@ -2252,9 +2189,6 @@
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="2:8" ht="18.75">
-      <c r="B38" t="s">
-        <v>95</v>
-      </c>
       <c r="C38"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -2263,9 +2197,6 @@
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="2:8" ht="18.75">
-      <c r="B39" t="s">
-        <v>85</v>
-      </c>
       <c r="C39"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -2274,9 +2205,6 @@
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="2:8" ht="18.75">
-      <c r="B40" t="s">
-        <v>96</v>
-      </c>
       <c r="C40"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -2453,7 +2381,7 @@
       <c r="H61" s="6"/>
     </row>
     <row r="62" spans="3:8" ht="18.75">
-      <c r="C62"/>
+      <c r="C62" s="6"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
@@ -2477,7 +2405,7 @@
       <c r="H64" s="6"/>
     </row>
     <row r="65" spans="3:8" ht="18.75">
-      <c r="C65" s="6"/>
+      <c r="C65"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
@@ -2669,28 +2597,28 @@
       <c r="H88" s="6"/>
     </row>
     <row r="89" spans="3:8" ht="18.75">
-      <c r="C89"/>
-      <c r="D89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="47"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
-      <c r="H89" s="6"/>
+      <c r="H89" s="4"/>
     </row>
     <row r="90" spans="3:8" ht="18.75">
-      <c r="C90"/>
-      <c r="D90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="47"/>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
-      <c r="H90" s="6"/>
+      <c r="H90" s="4"/>
     </row>
     <row r="91" spans="3:8" ht="18.75">
-      <c r="C91"/>
-      <c r="D91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="47"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
-      <c r="H91" s="6"/>
+      <c r="H91" s="4"/>
     </row>
     <row r="92" spans="3:8" ht="18.75">
       <c r="C92" s="4"/>
@@ -2701,20 +2629,20 @@
       <c r="H92" s="4"/>
     </row>
     <row r="93" spans="3:8" ht="18.75">
-      <c r="C93" s="4"/>
-      <c r="D93" s="47"/>
+      <c r="C93"/>
+      <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
+      <c r="H93" s="6"/>
     </row>
     <row r="94" spans="3:8" ht="18.75">
-      <c r="C94" s="4"/>
-      <c r="D94" s="47"/>
+      <c r="C94"/>
+      <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
+      <c r="H94" s="6"/>
     </row>
     <row r="95" spans="3:8" ht="18.75">
       <c r="C95" s="4"/>
@@ -2722,7 +2650,7 @@
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
+      <c r="H95" s="6"/>
     </row>
     <row r="96" spans="3:8" ht="18.75">
       <c r="C96"/>
@@ -2741,41 +2669,17 @@
       <c r="H97" s="6"/>
     </row>
     <row r="98" spans="3:8" ht="18.75">
-      <c r="C98" s="4"/>
-      <c r="D98" s="47"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="6"/>
+      <c r="C98" s="43"/>
+      <c r="D98" s="39"/>
+      <c r="H98" s="36"/>
     </row>
     <row r="99" spans="3:8" ht="18.75">
-      <c r="C99"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="6"/>
-    </row>
-    <row r="100" spans="3:8" ht="18.75">
-      <c r="C100"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="6"/>
-    </row>
-    <row r="101" spans="3:8" ht="18.75">
-      <c r="C101" s="43"/>
-      <c r="D101" s="39"/>
-      <c r="H101" s="36"/>
-    </row>
-    <row r="102" spans="3:8" ht="18.75">
-      <c r="C102" s="43"/>
-      <c r="D102" s="39"/>
-      <c r="H102" s="36"/>
+      <c r="C99" s="43"/>
+      <c r="D99" s="39"/>
+      <c r="H99" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="E2:G102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E2:G99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -2786,19 +2690,19 @@
           <x14:formula1>
             <xm:f>プルダウン用!$B$3:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G96:G97 G99:G1048576 G1:G91</xm:sqref>
+          <xm:sqref>G93:G94 G96:G1048576 G1:G88</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
             <xm:f>プルダウン用!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F99:F1048576 F1:F97</xm:sqref>
+          <xm:sqref>F96:F1048576 F1:F94</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
             <xm:f>プルダウン用!$F$3:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E96:E97 E99:E1048576 E1:E91</xm:sqref>
+          <xm:sqref>E93:E94 E96:E1048576 E1:E88</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3225,21 +3129,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3377,24 +3266,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3410,4 +3297,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB5C4D7-D386-4D57-A2C8-4C67C79646A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05161D6-7E73-425A-A1D1-3BAF96401034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="1065" windowWidth="22950" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3129,6 +3129,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3266,22 +3281,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3297,21 +3314,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05161D6-7E73-425A-A1D1-3BAF96401034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BA4372-0918-4813-834F-3AE57C2EA4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="1065" windowWidth="22950" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="プルダウン用" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">集計!$B$2:$G$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
   <si>
     <t>分類</t>
   </si>
@@ -564,16 +564,6 @@
     </rPh>
     <rPh sb="31" eb="33">
       <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デバックメニューのウィンドウモードをオンするとマウスカーソルが消えてしまう不具合</t>
-    <rPh sb="31" eb="32">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="37" eb="40">
-      <t>フグアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1591,7 +1581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I99"/>
+  <dimension ref="B1:I98"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -2091,7 +2081,7 @@
     </row>
     <row r="29" spans="2:8" ht="18.75">
       <c r="B29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C29"/>
       <c r="D29" s="4"/>
@@ -2102,7 +2092,7 @@
     </row>
     <row r="30" spans="2:8" ht="18.75">
       <c r="B30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C30"/>
       <c r="D30" s="4"/>
@@ -2113,14 +2103,14 @@
     </row>
     <row r="31" spans="2:8" ht="18.75">
       <c r="B31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C31"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="H31" s="6"/>
     </row>
     <row r="32" spans="2:8" ht="18.75">
       <c r="B32" t="s">
@@ -2157,7 +2147,7 @@
     </row>
     <row r="35" spans="2:8" ht="18.75">
       <c r="B35" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C35"/>
       <c r="D35" s="4"/>
@@ -2168,7 +2158,7 @@
     </row>
     <row r="36" spans="2:8" ht="18.75">
       <c r="B36" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C36"/>
       <c r="D36" s="4"/>
@@ -2178,9 +2168,6 @@
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="2:8" ht="18.75">
-      <c r="B37" t="s">
-        <v>93</v>
-      </c>
       <c r="C37"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -2373,7 +2360,7 @@
       <c r="H60" s="6"/>
     </row>
     <row r="61" spans="3:8" ht="18.75">
-      <c r="C61"/>
+      <c r="C61" s="6"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -2381,7 +2368,7 @@
       <c r="H61" s="6"/>
     </row>
     <row r="62" spans="3:8" ht="18.75">
-      <c r="C62" s="6"/>
+      <c r="C62"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
@@ -2589,12 +2576,12 @@
       <c r="H87" s="6"/>
     </row>
     <row r="88" spans="3:8" ht="18.75">
-      <c r="C88"/>
-      <c r="D88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="47"/>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
-      <c r="H88" s="6"/>
+      <c r="H88" s="4"/>
     </row>
     <row r="89" spans="3:8" ht="18.75">
       <c r="C89" s="4"/>
@@ -2621,12 +2608,12 @@
       <c r="H91" s="4"/>
     </row>
     <row r="92" spans="3:8" ht="18.75">
-      <c r="C92" s="4"/>
-      <c r="D92" s="47"/>
+      <c r="C92"/>
+      <c r="D92" s="4"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
+      <c r="H92" s="6"/>
     </row>
     <row r="93" spans="3:8" ht="18.75">
       <c r="C93"/>
@@ -2637,16 +2624,16 @@
       <c r="H93" s="6"/>
     </row>
     <row r="94" spans="3:8" ht="18.75">
-      <c r="C94"/>
-      <c r="D94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="47"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
       <c r="H94" s="6"/>
     </row>
     <row r="95" spans="3:8" ht="18.75">
-      <c r="C95" s="4"/>
-      <c r="D95" s="47"/>
+      <c r="C95"/>
+      <c r="D95" s="4"/>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
@@ -2661,25 +2648,17 @@
       <c r="H96" s="6"/>
     </row>
     <row r="97" spans="3:8" ht="18.75">
-      <c r="C97"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="6"/>
+      <c r="C97" s="43"/>
+      <c r="D97" s="39"/>
+      <c r="H97" s="36"/>
     </row>
     <row r="98" spans="3:8" ht="18.75">
       <c r="C98" s="43"/>
       <c r="D98" s="39"/>
       <c r="H98" s="36"/>
     </row>
-    <row r="99" spans="3:8" ht="18.75">
-      <c r="C99" s="43"/>
-      <c r="D99" s="39"/>
-      <c r="H99" s="36"/>
-    </row>
   </sheetData>
-  <autoFilter ref="E2:G99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E2:G98" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -2690,19 +2669,19 @@
           <x14:formula1>
             <xm:f>プルダウン用!$B$3:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G93:G94 G96:G1048576 G1:G88</xm:sqref>
+          <xm:sqref>G92:G93 G95:G1048576 G1:G87</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
             <xm:f>プルダウン用!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F96:F1048576 F1:F94</xm:sqref>
+          <xm:sqref>F95:F1048576 F1:F93</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
             <xm:f>プルダウン用!$F$3:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E93:E94 E96:E1048576 E1:E88</xm:sqref>
+          <xm:sqref>E92:E93 E95:E1048576 E1:E87</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3129,21 +3108,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3281,24 +3245,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3314,4 +3276,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表作展後.xlsx
+++ b/コスト表作展後.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BA4372-0918-4813-834F-3AE57C2EA4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76FC92A-8372-47CD-8389-4F16DB826986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="1065" windowWidth="22950" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6675" yWindow="2655" windowWidth="20565" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="プルダウン用" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">集計!$B$2:$G$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>分類</t>
   </si>
@@ -434,22 +434,6 @@
   </si>
   <si>
     <t>チュートリアル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲームオーバー、クリアリザルトの倒した敵の数があっていない不具合</t>
-    <rPh sb="16" eb="17">
-      <t>タオ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カズ</t>
-    </rPh>
-    <rPh sb="29" eb="32">
-      <t>フグアイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1581,7 +1565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I98"/>
+  <dimension ref="B1:I97"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -1688,10 +1672,10 @@
     </row>
     <row r="6" spans="2:8" ht="18.75">
       <c r="B6" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="36" t="s">
         <v>82</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>83</v>
       </c>
       <c r="D6" s="39">
         <v>0.5</v>
@@ -1706,10 +1690,10 @@
     </row>
     <row r="7" spans="2:8" ht="18.75">
       <c r="B7" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" s="39">
         <v>1</v>
@@ -1737,7 +1721,7 @@
       </c>
       <c r="F8" s="40"/>
       <c r="G8" s="40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H8" s="45" t="s">
         <v>53</v>
@@ -1814,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H12" s="43" t="s">
         <v>56</v>
@@ -1834,7 +1818,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" s="43" t="s">
         <v>59</v>
@@ -1854,7 +1838,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H14" s="43" t="s">
         <v>60</v>
@@ -1893,7 +1877,7 @@
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H16" s="46" t="s">
         <v>57</v>
@@ -2037,7 +2021,7 @@
     </row>
     <row r="25" spans="2:8" ht="18.75">
       <c r="B25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="4"/>
@@ -2048,18 +2032,18 @@
     </row>
     <row r="26" spans="2:8" ht="18.75">
       <c r="B26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C26"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="6"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="2:8" ht="18.75">
       <c r="B27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C27"/>
       <c r="D27" s="4"/>
@@ -2070,7 +2054,7 @@
     </row>
     <row r="28" spans="2:8" ht="18.75">
       <c r="B28" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C28"/>
       <c r="D28" s="4"/>
@@ -2081,7 +2065,7 @@
     </row>
     <row r="29" spans="2:8" ht="18.75">
       <c r="B29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C29"/>
       <c r="D29" s="4"/>
@@ -2092,14 +2076,14 @@
     </row>
     <row r="30" spans="2:8" ht="18.75">
       <c r="B30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C30"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" spans="2:8" ht="18.75">
       <c r="B31" t="s">
@@ -2136,7 +2120,7 @@
     </row>
     <row r="34" spans="2:8" ht="18.75">
       <c r="B34" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C34"/>
       <c r="D34" s="4"/>
@@ -2147,7 +2131,7 @@
     </row>
     <row r="35" spans="2:8" ht="18.75">
       <c r="B35" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C35"/>
       <c r="D35" s="4"/>
@@ -2157,9 +2141,6 @@
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="2:8" ht="18.75">
-      <c r="B36" t="s">
-        <v>92</v>
-      </c>
       <c r="C36"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -2352,7 +2333,7 @@
       <c r="H59" s="6"/>
     </row>
     <row r="60" spans="3:8" ht="18.75">
-      <c r="C60"/>
+      <c r="C60" s="6"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
@@ -2360,7 +2341,7 @@
       <c r="H60" s="6"/>
     </row>
     <row r="61" spans="3:8" ht="18.75">
-      <c r="C61" s="6"/>
+      <c r="C61"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -2568,12 +2549,12 @@
       <c r="H86" s="6"/>
     </row>
     <row r="87" spans="3:8" ht="18.75">
-      <c r="C87"/>
-      <c r="D87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="47"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
-      <c r="H87" s="6"/>
+      <c r="H87" s="4"/>
     </row>
     <row r="88" spans="3:8" ht="18.75">
       <c r="C88" s="4"/>
@@ -2600,12 +2581,12 @@
       <c r="H90" s="4"/>
     </row>
     <row r="91" spans="3:8" ht="18.75">
-      <c r="C91" s="4"/>
-      <c r="D91" s="47"/>
+      <c r="C91"/>
+      <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
+      <c r="H91" s="6"/>
     </row>
     <row r="92" spans="3:8" ht="18.75">
       <c r="C92"/>
@@ -2616,16 +2597,16 @@
       <c r="H92" s="6"/>
     </row>
     <row r="93" spans="3:8" ht="18.75">
-      <c r="C93"/>
-      <c r="D93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="47"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
       <c r="H93" s="6"/>
     </row>
     <row r="94" spans="3:8" ht="18.75">
-      <c r="C94" s="4"/>
-      <c r="D94" s="47"/>
+      <c r="C94"/>
+      <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
@@ -2640,25 +2621,17 @@
       <c r="H95" s="6"/>
     </row>
     <row r="96" spans="3:8" ht="18.75">
-      <c r="C96"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="6"/>
+      <c r="C96" s="43"/>
+      <c r="D96" s="39"/>
+      <c r="H96" s="36"/>
     </row>
     <row r="97" spans="3:8" ht="18.75">
       <c r="C97" s="43"/>
       <c r="D97" s="39"/>
       <c r="H97" s="36"/>
     </row>
-    <row r="98" spans="3:8" ht="18.75">
-      <c r="C98" s="43"/>
-      <c r="D98" s="39"/>
-      <c r="H98" s="36"/>
-    </row>
   </sheetData>
-  <autoFilter ref="E2:G98" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E2:G97" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -2669,19 +2642,19 @@
           <x14:formula1>
             <xm:f>プルダウン用!$B$3:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G92:G93 G95:G1048576 G1:G87</xm:sqref>
+          <xm:sqref>G91:G92 G94:G1048576 G1:G86</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
             <xm:f>プルダウン用!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F95:F1048576 F1:F93</xm:sqref>
+          <xm:sqref>F94:F1048576 F1:F92</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
             <xm:f>プルダウン用!$F$3:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E92:E93 E95:E1048576 E1:E87</xm:sqref>
+          <xm:sqref>E91:E92 E94:E1048576 E1:E86</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2746,7 +2719,7 @@
       </c>
       <c r="D3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "完了")</f>
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="E3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "作業中")</f>
@@ -2754,18 +2727,18 @@
       </c>
       <c r="F3" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="13">
         <f>SUMIF(コスト表!G:G,"完了",コスト表!D:D)</f>
-        <v>14.5</v>
+        <v>22.5</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>18</v>
@@ -2782,30 +2755,30 @@
       </c>
       <c r="D4" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "完了")</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E4" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "作業中")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="28">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵", コスト表!G:G, "未着手")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="24">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵") * 100,1)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I4" s="16" t="s">
         <v>19</v>
       </c>
       <c r="J4" s="13">
         <f ca="1">NETWORKDAYS(J5,J6)</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K4" s="13">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="M4" s="12"/>
     </row>
@@ -2873,7 +2846,7 @@
       </c>
       <c r="J6" s="26">
         <f ca="1">TODAY()</f>
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="12"/>
@@ -2970,7 +2943,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="24">
         <f>ROUNDDOWN(COUNTIF(コスト表!G:G, "完了") / COUNTA(コスト表!G:G) * 100,1)</f>
-        <v>63.6</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -3108,6 +3081,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -3245,22 +3233,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3276,21 +3266,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>